--- a/04_DESIGN_TABLES/DesignTable_6801.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6801.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AD102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -625,6 +625,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -7586,12 +7591,17 @@
       </c>
       <c r="Z72" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p041-t01: agrees on LEG_ORB@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>6801-16-12-NWO-FG</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7782,7 @@
       </c>
       <c r="X74" s="4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="Y74" s="4" t="inlineStr">
@@ -7782,12 +7792,17 @@
       </c>
       <c r="Z74" s="4" t="inlineStr">
         <is>
-          <t>ORB -14 groove width UNPUBLISHED and unmeasured | DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>ORB -14 groove width UNPUBLISHED and unmeasured | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p041-t01: agrees on LEG_ORB@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>6801-16-14-NWO-FG</t>
         </is>
       </c>
     </row>
@@ -7978,12 +7993,17 @@
       </c>
       <c r="Z76" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p041-t01: agrees on LEG_ORB@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>6801-16-16-NWO-FG</t>
         </is>
       </c>
     </row>
@@ -10165,6 +10185,115 @@
       <c r="AC101" t="inlineStr">
         <is>
           <t>6801-24-32-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>6801-16-10-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F102" t="n">
+        <v>60</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="K102" t="n">
+        <v>37</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="P102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="T102" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>6801-16-10-NWO-FG</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>7/8-14</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / locknut hex / bores / flats from the Brennan TFA catalog p.41; JIC end MS33656J; adjustable ORB end data from the table's own -10 ORB rows (A5)</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.41 alone; JIC end chain + ORB end data from the libraries / same-ORB-size rows; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>6801-16-10-NWO-FG</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
